--- a/data/trans_dic/P33B_R4-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R4-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,84</t>
+          <t>2,06; 6,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,61</t>
+          <t>5,62; 10,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,7</t>
+          <t>4,34; 7,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,83</t>
+          <t>4,84; 10,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,79</t>
+          <t>10,95; 16,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 12,55</t>
+          <t>8,74; 12,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 20,44</t>
+          <t>13,33; 21,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 23,5</t>
+          <t>16,98; 23,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 21,05</t>
+          <t>16,08; 21,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,57; 23,93</t>
+          <t>12,73; 23,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 26,74</t>
+          <t>22,16; 30,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 23,73</t>
+          <t>18,91; 25,39</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,59</t>
+          <t>4,94; 11,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 14,99</t>
+          <t>9,27; 14,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,2</t>
+          <t>7,74; 11,65</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,89; 18,51</t>
+          <t>10,82; 18,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,48; 28,56</t>
+          <t>20,42; 28,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,7; 21,9</t>
+          <t>16,65; 21,75</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,89; 17,54</t>
+          <t>11,83; 18,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,09; 28,33</t>
+          <t>24,88; 31,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,05; 21,51</t>
+          <t>19,67; 23,95</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 22,13</t>
+          <t>17,65; 23,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,25; 34,75</t>
+          <t>27,98; 33,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,81; 27,27</t>
+          <t>23,8; 27,75</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,22</t>
+          <t>12,67; 15,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,93; 22,58</t>
+          <t>21,39; 23,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,19</t>
+          <t>17,5; 19,13</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34518</t>
+          <t>36514</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6574; 21305</t>
+          <t>6565; 19936</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16143; 30718</t>
+          <t>17775; 32010</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25215; 46257</t>
+          <t>27570; 46509</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>73067</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109100</t>
+          <t>110995</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25451; 50945</t>
+          <t>25665; 53081</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59348; 86380</t>
+          <t>59749; 87521</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90208; 129561</t>
+          <t>94072; 132421</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>53211</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69552</t>
+          <t>71995</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120754</t>
+          <t>125207</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39024; 64182</t>
+          <t>41853; 67484</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58545; 82030</t>
+          <t>60514; 84630</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105326; 139615</t>
+          <t>107796; 144733</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>57274</t>
+          <t>64535</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99221</t>
+          <t>108924</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156495</t>
+          <t>173460</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42423; 74780</t>
+          <t>47511; 86096</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57502; 127097</t>
+          <t>93401; 127819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112358; 186982</t>
+          <t>150250; 201753</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>41837</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9743; 20711</t>
+          <t>10165; 23289</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18939; 31226</t>
+          <t>21034; 33923</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30766; 47205</t>
+          <t>33492; 50402</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62035</t>
+          <t>64118</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100693</t>
+          <t>102354</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29358; 49913</t>
+          <t>29281; 49893</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52648; 73408</t>
+          <t>53848; 74687</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87962; 115328</t>
+          <t>88998; 116256</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>87535</t>
+          <t>105241</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>176016</t>
+          <t>216180</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263550</t>
+          <t>321422</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>67858; 109303</t>
+          <t>84986; 131875</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>85703; 240594</t>
+          <t>192064; 241143</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177484; 316694</t>
+          <t>293267; 357028</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>144085</t>
+          <t>161019</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>227859</t>
+          <t>255731</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>371943</t>
+          <t>416750</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>67830; 205483</t>
+          <t>140862; 183767</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>209266; 248594</t>
+          <t>232436; 277481</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>226997; 448424</t>
+          <t>387545; 451926</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>442807</t>
+          <t>487850</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>752955</t>
+          <t>840688</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1195762</t>
+          <t>1328538</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>340557; 491671</t>
+          <t>447367; 536492</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>619270; 825994</t>
+          <t>798390; 882710</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1026657; 1294178</t>
+          <t>1270891; 1389085</t>
         </is>
       </c>
     </row>
